--- a/Final_results/PerformanceSA.xlsx
+++ b/Final_results/PerformanceSA.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enstafr-my.sharepoint.com/personal/christopher_tsa_ensta-paris_fr/Documents/ENSTA/3A/Metaheuristique/project/final_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2FAC0D2E-242A-1A4D-B389-A220C35E545E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{2FAC0D2E-242A-1A4D-B389-A220C35E545E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B812D4D4-78EB-4049-862F-5FEAD7DADA2B}"/>
   <bookViews>
-    <workbookView xWindow="31900" yWindow="-7700" windowWidth="27240" windowHeight="15940" xr2:uid="{5291BE0A-BBF2-824B-BC3A-017B99172BFD}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{5291BE0A-BBF2-824B-BC3A-017B99172BFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -738,7 +738,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -747,11 +747,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1091,7 +1092,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="18.6640625" customWidth="1"/>
-    <col min="4" max="4" width="22.1640625" customWidth="1"/>
+    <col min="4" max="4" width="22.1640625" style="11" customWidth="1"/>
     <col min="5" max="5" width="22.33203125" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
     <col min="7" max="7" width="22.6640625" customWidth="1"/>
@@ -1108,7 +1109,7 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -1134,7 +1135,7 @@
       <c r="C2">
         <v>100</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="11">
         <v>5</v>
       </c>
       <c r="E2" t="s">
@@ -1160,7 +1161,7 @@
       <c r="C3">
         <v>100</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="11">
         <v>5</v>
       </c>
       <c r="E3" t="s">
@@ -1186,7 +1187,7 @@
       <c r="C4">
         <v>100</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="11">
         <v>5</v>
       </c>
       <c r="E4" t="s">
@@ -1212,7 +1213,7 @@
       <c r="C5">
         <v>100</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="11">
         <v>5</v>
       </c>
       <c r="E5" t="s">
@@ -1238,7 +1239,7 @@
       <c r="C6">
         <v>100</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="11">
         <v>5</v>
       </c>
       <c r="E6" t="s">
@@ -1264,7 +1265,7 @@
       <c r="C7">
         <v>100</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="11">
         <v>5</v>
       </c>
       <c r="E7" t="s">
@@ -1290,7 +1291,7 @@
       <c r="C8">
         <v>100</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="11">
         <v>5</v>
       </c>
       <c r="E8" t="s">
@@ -1316,7 +1317,7 @@
       <c r="C9">
         <v>100</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="11">
         <v>5</v>
       </c>
       <c r="E9" t="s">
@@ -1342,7 +1343,7 @@
       <c r="C10">
         <v>100</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="11">
         <v>5</v>
       </c>
       <c r="E10" t="s">
@@ -1368,7 +1369,7 @@
       <c r="C11">
         <v>100</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="11">
         <v>5</v>
       </c>
       <c r="E11" t="s">
@@ -1394,7 +1395,7 @@
       <c r="C12">
         <v>250</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="11">
         <v>5</v>
       </c>
       <c r="E12" t="s">
@@ -1420,7 +1421,7 @@
       <c r="C13">
         <v>250</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="11">
         <v>5</v>
       </c>
       <c r="E13" t="s">
@@ -1446,7 +1447,7 @@
       <c r="C14">
         <v>250</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="11">
         <v>5</v>
       </c>
       <c r="E14" t="s">
@@ -1472,7 +1473,7 @@
       <c r="C15">
         <v>250</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="11">
         <v>5</v>
       </c>
       <c r="E15" t="s">
@@ -1498,7 +1499,7 @@
       <c r="C16">
         <v>250</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="11">
         <v>5</v>
       </c>
       <c r="E16" t="s">
@@ -1507,7 +1508,7 @@
       <c r="F16" t="s">
         <v>130</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="10">
         <v>1.45544604841308E-2</v>
       </c>
       <c r="H16" s="5">
@@ -1524,7 +1525,7 @@
       <c r="C17">
         <v>250</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="11">
         <v>5</v>
       </c>
       <c r="E17" t="s">
@@ -1533,7 +1534,7 @@
       <c r="F17" t="s">
         <v>131</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="10">
         <v>5.1768349540428901E-2</v>
       </c>
       <c r="H17" s="5">
@@ -1550,7 +1551,7 @@
       <c r="C18">
         <v>250</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="11">
         <v>5</v>
       </c>
       <c r="E18" t="s">
@@ -1559,7 +1560,7 @@
       <c r="F18" t="s">
         <v>132</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="10">
         <v>2.4034164266560701E-2</v>
       </c>
       <c r="H18" s="5">
@@ -1576,7 +1577,7 @@
       <c r="C19">
         <v>250</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="11">
         <v>5</v>
       </c>
       <c r="E19" t="s">
@@ -1585,7 +1586,7 @@
       <c r="F19" t="s">
         <v>133</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="10">
         <v>2.8354372722540301E-2</v>
       </c>
       <c r="H19" s="5">
@@ -1602,7 +1603,7 @@
       <c r="C20">
         <v>250</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="11">
         <v>5</v>
       </c>
       <c r="E20" t="s">
@@ -1611,7 +1612,7 @@
       <c r="F20" t="s">
         <v>134</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="10">
         <v>2.46909590369233E-2</v>
       </c>
       <c r="H20" s="5">
@@ -1628,7 +1629,7 @@
       <c r="C21">
         <v>250</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="11">
         <v>5</v>
       </c>
       <c r="E21" t="s">
@@ -1654,7 +1655,7 @@
       <c r="C22">
         <v>500</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="11">
         <v>5</v>
       </c>
       <c r="E22" t="s">
@@ -1680,7 +1681,7 @@
       <c r="C23">
         <v>500</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="11">
         <v>5</v>
       </c>
       <c r="E23" t="s">
@@ -1706,7 +1707,7 @@
       <c r="C24">
         <v>500</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="11">
         <v>5</v>
       </c>
       <c r="E24" t="s">
@@ -1732,7 +1733,7 @@
       <c r="C25">
         <v>500</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="11">
         <v>5</v>
       </c>
       <c r="E25" t="s">
@@ -1758,7 +1759,7 @@
       <c r="C26">
         <v>500</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="11">
         <v>5</v>
       </c>
       <c r="E26" t="s">
@@ -1784,7 +1785,7 @@
       <c r="C27">
         <v>500</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="11">
         <v>5</v>
       </c>
       <c r="E27" t="s">
@@ -1810,7 +1811,7 @@
       <c r="C28">
         <v>500</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="11">
         <v>5</v>
       </c>
       <c r="E28" t="s">
@@ -1819,7 +1820,7 @@
       <c r="F28" t="s">
         <v>142</v>
       </c>
-      <c r="G28" s="12">
+      <c r="G28" s="10">
         <v>1.80752730600354E-2</v>
       </c>
       <c r="H28" s="5">
@@ -1836,7 +1837,7 @@
       <c r="C29">
         <v>500</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="11">
         <v>5</v>
       </c>
       <c r="E29" t="s">
@@ -1862,7 +1863,7 @@
       <c r="C30">
         <v>500</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="11">
         <v>5</v>
       </c>
       <c r="E30" t="s">
@@ -1871,7 +1872,7 @@
       <c r="F30" t="s">
         <v>144</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="10">
         <v>3.2004935225169603E-2</v>
       </c>
       <c r="H30" s="5">
@@ -1888,7 +1889,7 @@
       <c r="C31">
         <v>500</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="11">
         <v>5</v>
       </c>
       <c r="E31" t="s">
@@ -1914,7 +1915,7 @@
       <c r="C32">
         <v>100</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="11">
         <v>10</v>
       </c>
       <c r="E32" t="s">
@@ -1940,7 +1941,7 @@
       <c r="C33">
         <v>100</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="11">
         <v>10</v>
       </c>
       <c r="E33" t="s">
@@ -1966,7 +1967,7 @@
       <c r="C34">
         <v>100</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="11">
         <v>10</v>
       </c>
       <c r="E34" t="s">
@@ -1975,7 +1976,7 @@
       <c r="F34" t="s">
         <v>148</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G34" s="10">
         <v>3.3889114816320898E-2</v>
       </c>
       <c r="H34" s="5">
@@ -1992,7 +1993,7 @@
       <c r="C35">
         <v>100</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="11">
         <v>10</v>
       </c>
       <c r="E35" t="s">
@@ -2018,7 +2019,7 @@
       <c r="C36">
         <v>100</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="11">
         <v>10</v>
       </c>
       <c r="E36" t="s">
@@ -2027,7 +2028,7 @@
       <c r="F36" t="s">
         <v>150</v>
       </c>
-      <c r="G36" s="12">
+      <c r="G36" s="10">
         <v>1.7977231770032E-2</v>
       </c>
       <c r="H36" s="5">
@@ -2044,7 +2045,7 @@
       <c r="C37">
         <v>100</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="11">
         <v>10</v>
       </c>
       <c r="E37" t="s">
@@ -2070,7 +2071,7 @@
       <c r="C38">
         <v>100</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="11">
         <v>10</v>
       </c>
       <c r="E38" t="s">
@@ -2096,7 +2097,7 @@
       <c r="C39">
         <v>100</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="11">
         <v>10</v>
       </c>
       <c r="E39" t="s">
@@ -2105,7 +2106,7 @@
       <c r="F39" t="s">
         <v>153</v>
       </c>
-      <c r="G39" s="12">
+      <c r="G39" s="10">
         <v>5.7477358073779503E-2</v>
       </c>
       <c r="H39" s="5">
@@ -2122,7 +2123,7 @@
       <c r="C40">
         <v>100</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="11">
         <v>10</v>
       </c>
       <c r="E40" t="s">
@@ -2148,7 +2149,7 @@
       <c r="C41">
         <v>100</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="11">
         <v>10</v>
       </c>
       <c r="E41" t="s">
@@ -2157,7 +2158,7 @@
       <c r="F41" t="s">
         <v>155</v>
       </c>
-      <c r="G41" s="12">
+      <c r="G41" s="10">
         <v>3.0569993833142399E-2</v>
       </c>
       <c r="H41" s="5">
@@ -2174,7 +2175,7 @@
       <c r="C42">
         <v>250</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="11">
         <v>10</v>
       </c>
       <c r="E42" t="s">
@@ -2200,7 +2201,7 @@
       <c r="C43">
         <v>250</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="11">
         <v>10</v>
       </c>
       <c r="E43" t="s">
@@ -2226,7 +2227,7 @@
       <c r="C44">
         <v>250</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="11">
         <v>10</v>
       </c>
       <c r="E44" t="s">
@@ -2252,7 +2253,7 @@
       <c r="C45">
         <v>250</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="11">
         <v>10</v>
       </c>
       <c r="E45" t="s">
@@ -2278,7 +2279,7 @@
       <c r="C46">
         <v>250</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="11">
         <v>10</v>
       </c>
       <c r="E46" t="s">
@@ -2304,7 +2305,7 @@
       <c r="C47">
         <v>250</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="11">
         <v>10</v>
       </c>
       <c r="E47" t="s">
@@ -2330,7 +2331,7 @@
       <c r="C48">
         <v>250</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="11">
         <v>10</v>
       </c>
       <c r="E48" t="s">
@@ -2339,7 +2340,7 @@
       <c r="F48" t="s">
         <v>162</v>
       </c>
-      <c r="G48" s="12">
+      <c r="G48" s="10">
         <v>2.7727063320081201E-2</v>
       </c>
       <c r="H48" s="5">
@@ -2356,7 +2357,7 @@
       <c r="C49">
         <v>250</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="11">
         <v>10</v>
       </c>
       <c r="E49" t="s">
@@ -2365,7 +2366,7 @@
       <c r="F49" t="s">
         <v>163</v>
       </c>
-      <c r="G49" s="12">
+      <c r="G49" s="10">
         <v>4.7201996028311002E-2</v>
       </c>
       <c r="H49" s="5">
@@ -2382,7 +2383,7 @@
       <c r="C50">
         <v>250</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="11">
         <v>10</v>
       </c>
       <c r="E50" t="s">
@@ -2391,7 +2392,7 @@
       <c r="F50" t="s">
         <v>164</v>
       </c>
-      <c r="G50" s="12">
+      <c r="G50" s="10">
         <v>2.7583187390542899E-2</v>
       </c>
       <c r="H50">
@@ -2408,7 +2409,7 @@
       <c r="C51">
         <v>250</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="11">
         <v>10</v>
       </c>
       <c r="E51" t="s">
@@ -2417,7 +2418,7 @@
       <c r="F51" t="s">
         <v>165</v>
       </c>
-      <c r="G51" s="12">
+      <c r="G51" s="10">
         <v>3.1050968864561601E-2</v>
       </c>
       <c r="H51" s="5">
@@ -2434,7 +2435,7 @@
       <c r="C52">
         <v>500</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="11">
         <v>10</v>
       </c>
       <c r="E52" t="s">
@@ -2460,7 +2461,7 @@
       <c r="C53">
         <v>500</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="11">
         <v>10</v>
       </c>
       <c r="E53" t="s">
@@ -2469,7 +2470,7 @@
       <c r="F53" t="s">
         <v>167</v>
       </c>
-      <c r="G53" s="12">
+      <c r="G53" s="10">
         <v>1.82979544901333E-2</v>
       </c>
       <c r="H53" s="5">
@@ -2486,7 +2487,7 @@
       <c r="C54">
         <v>500</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="11">
         <v>10</v>
       </c>
       <c r="E54" t="s">
@@ -2512,7 +2513,7 @@
       <c r="C55">
         <v>500</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="11">
         <v>10</v>
       </c>
       <c r="E55" t="s">
@@ -2521,7 +2522,7 @@
       <c r="F55" t="s">
         <v>169</v>
       </c>
-      <c r="G55" s="12">
+      <c r="G55" s="10">
         <v>1.99828285719095E-2</v>
       </c>
       <c r="H55" s="5">
@@ -2538,7 +2539,7 @@
       <c r="C56">
         <v>500</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="11">
         <v>10</v>
       </c>
       <c r="E56" t="s">
@@ -2564,7 +2565,7 @@
       <c r="C57">
         <v>500</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="11">
         <v>10</v>
       </c>
       <c r="E57" t="s">
@@ -2573,7 +2574,7 @@
       <c r="F57" t="s">
         <v>171</v>
       </c>
-      <c r="G57" s="12">
+      <c r="G57" s="10">
         <v>1.9940730322969499E-2</v>
       </c>
       <c r="H57" s="5">
@@ -2590,7 +2591,7 @@
       <c r="C58">
         <v>500</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="11">
         <v>10</v>
       </c>
       <c r="E58" t="s">
@@ -2599,7 +2600,7 @@
       <c r="F58" t="s">
         <v>172</v>
       </c>
-      <c r="G58" s="12">
+      <c r="G58" s="10">
         <v>2.19960083173972E-2</v>
       </c>
       <c r="H58" s="5">
@@ -2616,7 +2617,7 @@
       <c r="C59">
         <v>500</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="11">
         <v>10</v>
       </c>
       <c r="E59" t="s">
@@ -2642,7 +2643,7 @@
       <c r="C60">
         <v>500</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="11">
         <v>10</v>
       </c>
       <c r="E60" t="s">
@@ -2651,7 +2652,7 @@
       <c r="F60" t="s">
         <v>174</v>
       </c>
-      <c r="G60" s="12">
+      <c r="G60" s="10">
         <v>6.0155036126983502E-2</v>
       </c>
       <c r="H60" s="5">
@@ -2668,7 +2669,7 @@
       <c r="C61">
         <v>500</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="11">
         <v>10</v>
       </c>
       <c r="E61" t="s">
@@ -2677,7 +2678,7 @@
       <c r="F61" t="s">
         <v>175</v>
       </c>
-      <c r="G61" s="12">
+      <c r="G61" s="10">
         <v>2.52256033578174E-2</v>
       </c>
       <c r="H61" s="5">
@@ -2694,7 +2695,7 @@
       <c r="C62">
         <v>100</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="11">
         <v>30</v>
       </c>
       <c r="E62" t="s">
@@ -2720,7 +2721,7 @@
       <c r="C63">
         <v>100</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="11">
         <v>30</v>
       </c>
       <c r="E63" t="s">
@@ -2746,7 +2747,7 @@
       <c r="C64">
         <v>100</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="11">
         <v>30</v>
       </c>
       <c r="E64" t="s">
@@ -2772,7 +2773,7 @@
       <c r="C65">
         <v>100</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="11">
         <v>30</v>
       </c>
       <c r="E65" t="s">
@@ -2798,7 +2799,7 @@
       <c r="C66">
         <v>100</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="11">
         <v>30</v>
       </c>
       <c r="E66" t="s">
@@ -2824,7 +2825,7 @@
       <c r="C67">
         <v>100</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="11">
         <v>30</v>
       </c>
       <c r="E67" t="s">
@@ -2850,7 +2851,7 @@
       <c r="C68">
         <v>100</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="11">
         <v>30</v>
       </c>
       <c r="E68" t="s">
@@ -2859,7 +2860,7 @@
       <c r="F68" t="s">
         <v>182</v>
       </c>
-      <c r="G68" s="12">
+      <c r="G68" s="10">
         <v>3.0689481168860899E-2</v>
       </c>
       <c r="H68">
@@ -2876,7 +2877,7 @@
       <c r="C69">
         <v>100</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="11">
         <v>30</v>
       </c>
       <c r="E69" t="s">
@@ -2902,7 +2903,7 @@
       <c r="C70">
         <v>100</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="11">
         <v>30</v>
       </c>
       <c r="E70" t="s">
@@ -2928,7 +2929,7 @@
       <c r="C71">
         <v>100</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="11">
         <v>30</v>
       </c>
       <c r="E71" t="s">
@@ -2937,7 +2938,7 @@
       <c r="F71" t="s">
         <v>185</v>
       </c>
-      <c r="G71" s="12">
+      <c r="G71" s="10">
         <v>4.8706095410570402E-2</v>
       </c>
       <c r="H71" s="5">
@@ -2954,7 +2955,7 @@
       <c r="C72">
         <v>250</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="11">
         <v>30</v>
       </c>
       <c r="E72" t="s">
@@ -2980,7 +2981,7 @@
       <c r="C73">
         <v>250</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="11">
         <v>30</v>
       </c>
       <c r="E73" t="s">
@@ -2989,7 +2990,7 @@
       <c r="F73" t="s">
         <v>187</v>
       </c>
-      <c r="G73" s="12">
+      <c r="G73" s="10">
         <v>4.4737473850269202E-2</v>
       </c>
       <c r="H73" s="5">
@@ -3006,7 +3007,7 @@
       <c r="C74">
         <v>250</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="11">
         <v>30</v>
       </c>
       <c r="E74" t="s">
@@ -3032,7 +3033,7 @@
       <c r="C75">
         <v>250</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="11">
         <v>30</v>
       </c>
       <c r="E75" t="s">
@@ -3041,7 +3042,7 @@
       <c r="F75" t="s">
         <v>189</v>
       </c>
-      <c r="G75" s="12">
+      <c r="G75" s="10">
         <v>2.41809260855037E-2</v>
       </c>
       <c r="H75" s="5">
@@ -3058,7 +3059,7 @@
       <c r="C76">
         <v>250</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="11">
         <v>30</v>
       </c>
       <c r="E76" t="s">
@@ -3067,7 +3068,7 @@
       <c r="F76" t="s">
         <v>190</v>
       </c>
-      <c r="G76" s="12">
+      <c r="G76" s="10">
         <v>3.5317593459181597E-2</v>
       </c>
       <c r="H76" s="5">
@@ -3084,7 +3085,7 @@
       <c r="C77">
         <v>250</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="11">
         <v>30</v>
       </c>
       <c r="E77" t="s">
@@ -3110,7 +3111,7 @@
       <c r="C78">
         <v>250</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="11">
         <v>30</v>
       </c>
       <c r="E78" t="s">
@@ -3119,7 +3120,7 @@
       <c r="F78" t="s">
         <v>192</v>
       </c>
-      <c r="G78" s="12">
+      <c r="G78" s="10">
         <v>3.4321040289916803E-2</v>
       </c>
       <c r="H78" s="5">
@@ -3136,7 +3137,7 @@
       <c r="C79">
         <v>250</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="11">
         <v>30</v>
       </c>
       <c r="E79" t="s">
@@ -3162,7 +3163,7 @@
       <c r="C80">
         <v>250</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="11">
         <v>30</v>
       </c>
       <c r="E80" t="s">
@@ -3171,7 +3172,7 @@
       <c r="F80" t="s">
         <v>194</v>
       </c>
-      <c r="G80" s="12">
+      <c r="G80" s="10">
         <v>4.5663451829671603E-2</v>
       </c>
       <c r="H80" s="5">
@@ -3188,7 +3189,7 @@
       <c r="C81">
         <v>250</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="11">
         <v>30</v>
       </c>
       <c r="E81" t="s">
@@ -3214,7 +3215,7 @@
       <c r="C82">
         <v>500</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="11">
         <v>30</v>
       </c>
       <c r="E82" t="s">
@@ -3240,7 +3241,7 @@
       <c r="C83">
         <v>500</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="11">
         <v>30</v>
       </c>
       <c r="E83" t="s">
@@ -3266,7 +3267,7 @@
       <c r="C84">
         <v>500</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="11">
         <v>30</v>
       </c>
       <c r="E84" t="s">
@@ -3292,7 +3293,7 @@
       <c r="C85">
         <v>500</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="11">
         <v>30</v>
       </c>
       <c r="E85" t="s">
@@ -3318,7 +3319,7 @@
       <c r="C86">
         <v>500</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="11">
         <v>30</v>
       </c>
       <c r="E86" t="s">
@@ -3344,7 +3345,7 @@
       <c r="C87">
         <v>500</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="11">
         <v>30</v>
       </c>
       <c r="E87" t="s">
@@ -3370,7 +3371,7 @@
       <c r="C88">
         <v>500</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="11">
         <v>30</v>
       </c>
       <c r="E88" t="s">
@@ -3396,7 +3397,7 @@
       <c r="C89">
         <v>500</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="11">
         <v>30</v>
       </c>
       <c r="E89" t="s">
@@ -3422,7 +3423,7 @@
       <c r="C90">
         <v>500</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="11">
         <v>30</v>
       </c>
       <c r="E90" t="s">
@@ -3448,7 +3449,7 @@
       <c r="C91">
         <v>500</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="11">
         <v>30</v>
       </c>
       <c r="E91" t="s">
@@ -3471,7 +3472,7 @@
       <c r="C99" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="D99" s="6" t="s">
+      <c r="D99" s="12" t="s">
         <v>197</v>
       </c>
       <c r="E99" s="6" t="s">
@@ -3482,11 +3483,11 @@
       <c r="C100" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="D100" s="8">
+      <c r="D100" s="13">
         <f>MIN(G2:G91)</f>
         <v>4.3452925996836696E-3</v>
       </c>
-      <c r="E100" s="9">
+      <c r="E100" s="8">
         <f>MIN(H2:H91)</f>
         <v>33.659386157989502</v>
       </c>
@@ -3495,11 +3496,11 @@
       <c r="C101" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="D101" s="8">
+      <c r="D101" s="13">
         <f>MAX(G2:G91)</f>
         <v>7.7500460489961301E-2</v>
       </c>
-      <c r="E101" s="10">
+      <c r="E101" s="9">
         <f>MAX(H2:H91)</f>
         <v>792.00049304962101</v>
       </c>
@@ -3508,11 +3509,11 @@
       <c r="C102" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D102" s="11">
+      <c r="D102" s="13">
         <f>AVERAGE(G2:G91)</f>
         <v>3.424132051546331E-2</v>
       </c>
-      <c r="E102" s="10">
+      <c r="E102" s="9">
         <f>AVERAGE(H2:H91)</f>
         <v>220.81401673422903</v>
       </c>
@@ -3521,11 +3522,11 @@
       <c r="C103" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="D103" s="11">
+      <c r="D103" s="13">
         <f>STDEV(G2:G91)</f>
         <v>1.4305166672114442E-2</v>
       </c>
-      <c r="E103" s="9">
+      <c r="E103" s="8">
         <f>STDEV(H2:H91)</f>
         <v>139.59509507653843</v>
       </c>
